--- a/tame_output/ON/bt/strategyON_20240822.xlsx
+++ b/tame_output/ON/bt/strategyON_20240822.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.3%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.9%</t>
+          <t>431.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.5%</t>
+          <t>-665.4%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.3%</t>
+          <t>-330.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.0%</t>
+          <t>-149.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.395100454743252</v>
+        <v>-4.349429197504399</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.044196327739588</v>
+        <v>2.062464830635129</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8601785471833986</v>
+        <v>0.8787805544000175</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.318700062260675</v>
+        <v>4.329861266590647</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.369907270241934</v>
+        <v>-4.324236013003081</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.089240538152173</v>
+        <v>2.107509041047714</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8853717316847169</v>
+        <v>0.9039737389013358</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.368782909573524</v>
+        <v>4.379944113903496</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.357853143328971</v>
+        <v>-4.312181886090118</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.087748756818796</v>
+        <v>2.106017259714337</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8974258585976798</v>
+        <v>0.9160278658142986</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.36970195362274</v>
+        <v>4.380863157952711</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.36447639001933</v>
+        <v>-4.318805132780477</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.086980088326789</v>
+        <v>2.10524859122233</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8908026119073214</v>
+        <v>0.9094046191239402</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.367608635792661</v>
+        <v>4.378769840122632</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.261595800490737</v>
+        <v>-4.215924543251884</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.140983350016108</v>
+        <v>2.159251852911649</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9936832014359143</v>
+        <v>1.012285208652533</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.442188015387699</v>
+        <v>4.45334921971767</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.285037839670824</v>
+        <v>-4.239366582431971</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.151809204517668</v>
+        <v>2.170077707413209</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9936832014359143</v>
+        <v>1.012285208652533</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.462390685561293</v>
+        <v>4.473551889891264</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.303110347962435</v>
+        <v>-4.257439090723582</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.144580201201023</v>
+        <v>2.162848704096564</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9936832014359143</v>
+        <v>1.012285208652533</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.462390685561293</v>
+        <v>4.473551889891264</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.534284141839067</v>
+        <v>-4.488612884600214</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.012362597243837</v>
+        <v>2.030631100139378</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9936832014359143</v>
+        <v>1.012285208652533</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.422642599154759</v>
+        <v>4.433803803484731</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.502998121298612</v>
+        <v>-4.457326864059759</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.031899624456959</v>
+        <v>2.0501681273525</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.02496922197637</v>
+        <v>1.043571229192989</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.448436830475973</v>
+        <v>4.459598034805945</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.349972729185327</v>
+        <v>-4.304301471946474</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.192280780875177</v>
+        <v>2.210549283770718</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.177994614089654</v>
+        <v>1.196596621306273</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.639423065316848</v>
+        <v>4.650584269646819</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.378280043058598</v>
+        <v>-4.332608785819745</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.368424080234161</v>
+        <v>2.386692583129702</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.177994614089654</v>
+        <v>1.196596621306273</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.82688929022514</v>
+        <v>4.838050494555111</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.54487326817212</v>
+        <v>-4.499202010933267</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.271189741542835</v>
+        <v>2.289458244438376</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.011401388976131</v>
+        <v>1.03000339619275</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.696336306511109</v>
+        <v>4.70749751084108</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.37180888878982</v>
+        <v>-4.326137631550967</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.344091895957472</v>
+        <v>2.362360398853014</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.011401388976131</v>
+        <v>1.03000339619275</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.700012709172826</v>
+        <v>4.711173913502797</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.342562908334124</v>
+        <v>-4.296891651095271</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.353408343263246</v>
+        <v>2.371676846158787</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.011401388976131</v>
+        <v>1.03000339619275</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.697630764296322</v>
+        <v>4.708791968626294</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.449488456211975</v>
+        <v>-4.403817198973122</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.30793136326974</v>
+        <v>2.326199866165282</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9044758410982799</v>
+        <v>0.9230778483148988</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.630768674727246</v>
+        <v>4.641929879057217</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.594507014719223</v>
+        <v>-4.54883575748037</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.251352742010075</v>
+        <v>2.269621244905617</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7594572825910314</v>
+        <v>0.7780592898076503</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.545186341766131</v>
+        <v>4.556347546096102</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.712848780503941</v>
+        <v>-4.667177523265088</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.303947274953941</v>
+        <v>2.322215777849483</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7701433211539215</v>
+        <v>0.7887453283705403</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.651529204161618</v>
+        <v>4.662690408491589</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.764259202824649</v>
+        <v>-4.718587945585796</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.281168803151597</v>
+        <v>2.299437306047138</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7701433211539215</v>
+        <v>0.7887453283705403</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.649314901287557</v>
+        <v>4.660476105617528</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.8436786540324</v>
+        <v>-4.798007396793547</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.249304150742786</v>
+        <v>2.267572653638327</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7701433211539215</v>
+        <v>0.7887453283705403</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.649218029361847</v>
+        <v>4.660379233691818</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.939141651949618</v>
+        <v>-4.893470394710765</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.211112845133942</v>
+        <v>2.229381348029484</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7701433211539215</v>
+        <v>0.7887453283705403</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.64921192291989</v>
+        <v>4.660373127249861</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.979161649993402</v>
+        <v>-4.933490392754549</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.19320124247904</v>
+        <v>2.211469745374581</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7301233231101376</v>
+        <v>0.7487253303267565</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.62329632065623</v>
+        <v>4.634457524986201</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.831171972203364</v>
+        <v>3.80487409627619</v>
       </c>
       <c r="C2063" t="n">
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.039648390213693</v>
+        <v>-5.038568061629213</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.174740364138649</v>
+        <v>2.175172495572441</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7301233231101376</v>
+        <v>0.7487253303267565</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.629030138403957</v>
+        <v>4.640191342733928</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240822.xlsx
+++ b/tame_output/ON/bt/strategyON_20240822.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-46.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-660.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-156.7%</t>
         </is>
       </c>
     </row>
@@ -49000,10 +49000,10 @@
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.038568061629213</v>
+        <v>-4.988859554886742</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.175172495572441</v>
+        <v>2.195055898269429</v>
       </c>
       <c r="F2063" t="n">
         <v>0.7487253303267565</v>

--- a/tame_output/ON/bt/strategyON_20240822.xlsx
+++ b/tame_output/ON/bt/strategyON_20240822.xlsx
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>

--- a/tame_output/ON/bt/strategyON_20240822.xlsx
+++ b/tame_output/ON/bt/strategyON_20240822.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>118.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-16.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2063"/>
+  <dimension ref="A1:G2064"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.80487409627619</v>
+        <v>3.736109598636269</v>
       </c>
       <c r="C2063" t="n">
         <v>4.190956144537874</v>
@@ -49010,6 +49010,29 @@
       </c>
       <c r="G2063" t="n">
         <v>4.640191342733928</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="2" t="n">
+        <v>45526</v>
+      </c>
+      <c r="B2064" t="n">
+        <v>3.803478452570858</v>
+      </c>
+      <c r="C2064" t="n">
+        <v>4.305249372597108</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>-4.988859554886742</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>2.195055898269429</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>0.7487253303267565</v>
+      </c>
+      <c r="G2064" t="n">
+        <v>4.298313169583476</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240822.xlsx
+++ b/tame_output/ON/bt/strategyON_20240822.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>107.4%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.0%</t>
+          <t>-46.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>431.0%</t>
+          <t>431.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.5%</t>
+          <t>-660.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-156.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.4%</t>
+          <t>-330.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-149.1%</t>
+          <t>-145.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.324236013003081</v>
+        <v>-4.286262873751333</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.107509041047714</v>
+        <v>2.122698296748414</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9039737389013358</v>
+        <v>0.9419468781530834</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.379944113903496</v>
+        <v>4.402727997454544</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.312181886090118</v>
+        <v>-4.27420874683837</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.106017259714337</v>
+        <v>2.121206515415036</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9160278658142986</v>
+        <v>0.9540010050660462</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.380863157952711</v>
+        <v>4.40364704150376</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.318805132780477</v>
+        <v>-4.280831993528729</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.10524859122233</v>
+        <v>2.120437846923029</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9094046191239402</v>
+        <v>0.9473777583756879</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.378769840122632</v>
+        <v>4.401553723673681</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.215924543251884</v>
+        <v>-4.177951404000136</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.159251852911649</v>
+        <v>2.174441108612348</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.012285208652533</v>
+        <v>1.050258347904281</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.45334921971767</v>
+        <v>4.476133103268719</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.239366582431971</v>
+        <v>-4.201393443180223</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.170077707413209</v>
+        <v>2.185266963113908</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.012285208652533</v>
+        <v>1.050258347904281</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.473551889891264</v>
+        <v>4.496335773442313</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.257439090723582</v>
+        <v>-4.219465951471834</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.162848704096564</v>
+        <v>2.178037959797264</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.012285208652533</v>
+        <v>1.050258347904281</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.473551889891264</v>
+        <v>4.496335773442313</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.488612884600214</v>
+        <v>-4.450639745348466</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.030631100139378</v>
+        <v>2.045820355840077</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.012285208652533</v>
+        <v>1.050258347904281</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.433803803484731</v>
+        <v>4.45658768703578</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.457326864059759</v>
+        <v>-4.419353724808011</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.0501681273525</v>
+        <v>2.065357383053199</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.043571229192989</v>
+        <v>1.081544368444736</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.459598034805945</v>
+        <v>4.482381918356993</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.304301471946474</v>
+        <v>-4.266328332694727</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.210549283770718</v>
+        <v>2.225738539471417</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.196596621306273</v>
+        <v>1.23456976055802</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.650584269646819</v>
+        <v>4.673368153197868</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.332608785819745</v>
+        <v>-4.294635646567997</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.386692583129702</v>
+        <v>2.401881838830402</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.196596621306273</v>
+        <v>1.23456976055802</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.838050494555111</v>
+        <v>4.86083437810616</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.499202010933267</v>
+        <v>-4.461228871681519</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.289458244438376</v>
+        <v>2.304647500139075</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.03000339619275</v>
+        <v>1.067976535444498</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.70749751084108</v>
+        <v>4.730281394392128</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.326137631550967</v>
+        <v>-4.288164492299219</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.362360398853014</v>
+        <v>2.377549654553713</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.03000339619275</v>
+        <v>1.067976535444498</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.711173913502797</v>
+        <v>4.733957797053846</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.296891651095271</v>
+        <v>-4.258918511843523</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.371676846158787</v>
+        <v>2.386866101859487</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.03000339619275</v>
+        <v>1.067976535444498</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.708791968626294</v>
+        <v>4.731575852177341</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.403817198973122</v>
+        <v>-4.365844059721374</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.326199866165282</v>
+        <v>2.341389121865981</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9230778483148988</v>
+        <v>0.9610509875666463</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.641929879057217</v>
+        <v>4.664713762608266</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.54883575748037</v>
+        <v>-4.510862618228622</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.269621244905617</v>
+        <v>2.284810500606316</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7780592898076503</v>
+        <v>0.8160324290593978</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.556347546096102</v>
+        <v>4.579131429647151</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.667177523265088</v>
+        <v>-4.62920438401334</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.322215777849483</v>
+        <v>2.337405033550182</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7887453283705403</v>
+        <v>0.8267184676222878</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.662690408491589</v>
+        <v>4.685474292042638</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.718587945585796</v>
+        <v>-4.680614806334048</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.299437306047138</v>
+        <v>2.314626561747837</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7887453283705403</v>
+        <v>0.8267184676222878</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.660476105617528</v>
+        <v>4.683259989168577</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.798007396793547</v>
+        <v>-4.7600342575418</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.267572653638327</v>
+        <v>2.282761909339026</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7887453283705403</v>
+        <v>0.8267184676222878</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.660379233691818</v>
+        <v>4.683163117242866</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.893470394710765</v>
+        <v>-4.855497255459017</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.229381348029484</v>
+        <v>2.244570603730183</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7887453283705403</v>
+        <v>0.8267184676222878</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.660373127249861</v>
+        <v>4.68315701080091</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.933490392754549</v>
+        <v>-4.895517253502801</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.211469745374581</v>
+        <v>2.22665900107528</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7487253303267565</v>
+        <v>0.786698469578504</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.634457524986201</v>
+        <v>4.65724140853725</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636269</v>
+        <v>3.736109598636271</v>
       </c>
       <c r="C2063" t="n">
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.988859554886742</v>
+        <v>-4.950886415634995</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.195055898269429</v>
+        <v>2.210245153970129</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7487253303267565</v>
+        <v>0.786698469578504</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.640191342733928</v>
+        <v>4.662975226284977</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.803478452570858</v>
+        <v>3.815468926386238</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.305249372597108</v>
+        <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.988859554886742</v>
+        <v>-4.990752517251783</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.195055898269429</v>
+        <v>2.193837076666346</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7487253303267565</v>
+        <v>0.786698469578504</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.298313169583476</v>
+        <v>4.66251358962791</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240822.xlsx
+++ b/tame_output/ON/bt/strategyON_20240822.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>431.1%</t>
+          <t>431.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.6%</t>
+          <t>-666.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-159.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.3%</t>
+          <t>-330.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-145.3%</t>
+          <t>-152.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.349429197504399</v>
+        <v>-4.395100454743252</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.062464830635129</v>
+        <v>2.044196327739588</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8787805544000175</v>
+        <v>0.8601785471833986</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.329861266590647</v>
+        <v>4.318700062260675</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.286262873751333</v>
+        <v>-4.33976986684149</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.122698296748414</v>
+        <v>2.101295499512351</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9419468781530834</v>
+        <v>0.9155091350851607</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.402727997454544</v>
+        <v>4.386865351613791</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.27420874683837</v>
+        <v>-4.327715739928527</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.121206515415036</v>
+        <v>2.099803718178974</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9540010050660462</v>
+        <v>0.9275632619981236</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.40364704150376</v>
+        <v>4.387784395663006</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.280831993528729</v>
+        <v>-4.334338986618885</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.120437846923029</v>
+        <v>2.099035049686966</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9473777583756879</v>
+        <v>0.9209400153077651</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.401553723673681</v>
+        <v>4.385691077832927</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.177951404000136</v>
+        <v>-4.231458397090292</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.174441108612348</v>
+        <v>2.153038311376286</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.050258347904281</v>
+        <v>1.023820604836358</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.476133103268719</v>
+        <v>4.460270457427965</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.201393443180223</v>
+        <v>-4.254900436270379</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.185266963113908</v>
+        <v>2.163864165877845</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.050258347904281</v>
+        <v>1.023820604836358</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.496335773442313</v>
+        <v>4.480473127601559</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.219465951471834</v>
+        <v>-4.272972944561991</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.178037959797264</v>
+        <v>2.156635162561201</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.050258347904281</v>
+        <v>1.023820604836358</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.496335773442313</v>
+        <v>4.480473127601559</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.450639745348466</v>
+        <v>-4.504146738438623</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.045820355840077</v>
+        <v>2.024417558604015</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.050258347904281</v>
+        <v>1.023820604836358</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.45658768703578</v>
+        <v>4.440725041195027</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.419353724808011</v>
+        <v>-4.472860717898167</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.065357383053199</v>
+        <v>2.043954585817137</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.081544368444736</v>
+        <v>1.055106625376813</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.482381918356993</v>
+        <v>4.466519272516239</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.266328332694727</v>
+        <v>-4.319835325784883</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.225738539471417</v>
+        <v>2.204335742235354</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.23456976055802</v>
+        <v>1.208132017490097</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.673368153197868</v>
+        <v>4.657505507357113</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.294635646567997</v>
+        <v>-4.348142639658153</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.401881838830402</v>
+        <v>2.380479041594339</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.23456976055802</v>
+        <v>1.208132017490097</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.86083437810616</v>
+        <v>4.844971732265407</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.461228871681519</v>
+        <v>-4.514735864771676</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.304647500139075</v>
+        <v>2.283244702903012</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.067976535444498</v>
+        <v>1.041538792376575</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.730281394392128</v>
+        <v>4.714418748551375</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.288164492299219</v>
+        <v>-4.341671485389376</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.377549654553713</v>
+        <v>2.35614685731765</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.067976535444498</v>
+        <v>1.041538792376575</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.733957797053846</v>
+        <v>4.718095151213093</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.258918511843523</v>
+        <v>-4.312425504933679</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.386866101859487</v>
+        <v>2.365463304623424</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.067976535444498</v>
+        <v>1.041538792376575</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.731575852177341</v>
+        <v>4.715713206336588</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.365844059721374</v>
+        <v>-4.41935105281153</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.341389121865981</v>
+        <v>2.319986324629919</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9610509875666463</v>
+        <v>0.9346132444987235</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.664713762608266</v>
+        <v>4.648851116767512</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.510862618228622</v>
+        <v>-4.564369611318779</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.284810500606316</v>
+        <v>2.263407703370254</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8160324290593978</v>
+        <v>0.789594685991475</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.579131429647151</v>
+        <v>4.563268783806397</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.62920438401334</v>
+        <v>-4.682711377103496</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.337405033550182</v>
+        <v>2.31600223631412</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8267184676222878</v>
+        <v>0.8002807245543651</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.685474292042638</v>
+        <v>4.669611646201885</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.680614806334048</v>
+        <v>-4.734121799424204</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.314626561747837</v>
+        <v>2.293223764511775</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8267184676222878</v>
+        <v>0.8002807245543651</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.683259989168577</v>
+        <v>4.667397343327823</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.7600342575418</v>
+        <v>-4.813541250631956</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.282761909339026</v>
+        <v>2.261359112102964</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8267184676222878</v>
+        <v>0.8002807245543651</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.683163117242866</v>
+        <v>4.667300471402113</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.855497255459017</v>
+        <v>-4.909004248549174</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.244570603730183</v>
+        <v>2.22316780649412</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8267184676222878</v>
+        <v>0.8002807245543651</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.68315701080091</v>
+        <v>4.667294364960156</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.895517253502801</v>
+        <v>-4.949024246592957</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.22665900107528</v>
+        <v>2.205256203839217</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.786698469578504</v>
+        <v>0.7602607265105812</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.65724140853725</v>
+        <v>4.641378762696497</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636271</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.950886415634995</v>
+        <v>-5.004393408725151</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.210245153970129</v>
+        <v>2.188842356734066</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.786698469578504</v>
+        <v>0.7602607265105812</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.662975226284977</v>
+        <v>4.647112580444223</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.990752517251783</v>
+        <v>-5.044407999745439</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.193837076666346</v>
+        <v>2.172374883668884</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.786698469578504</v>
+        <v>0.7202492799034419</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.66251358962791</v>
+        <v>4.622644075822873</v>
       </c>
     </row>
   </sheetData>
